--- a/artfynd/A 53843-2025 artfynd.xlsx
+++ b/artfynd/A 53843-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7120231</v>
+        <v>7120156</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565042.0046425893</v>
+        <v>565042</v>
       </c>
       <c r="R2" t="n">
-        <v>6437847.870258086</v>
+        <v>6437848</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32777</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32775</t>
         </is>
       </c>
       <c r="AD2" t="b">
